--- a/extraction_script/data/اصلاحیه بودجه تفصیلی 98 - 991212 (1).xlsx
+++ b/extraction_script/data/اصلاحیه بودجه تفصیلی 98 - 991212 (1).xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armin KHoojavi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armin KHoojavi\Downloads\persian-smart-accounting1\extraction_script\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D0D32A-A077-4228-8F10-8654560A5AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6662AF-A024-41D9-8C01-13DCE7E2556F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="16200" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="فرم 1" sheetId="1" r:id="rId1"/>
-    <sheet name="فرم 2" sheetId="2" r:id="rId2"/>
-    <sheet name="فرم 3" sheetId="3" r:id="rId3"/>
-    <sheet name="فرم 4" sheetId="4" r:id="rId4"/>
-    <sheet name="فرم 5" sheetId="5" r:id="rId5"/>
-    <sheet name="فرم 6" sheetId="6" r:id="rId6"/>
-    <sheet name="فرم 8" sheetId="7" r:id="rId7"/>
-    <sheet name="فرم 9" sheetId="8" r:id="rId8"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
+    <sheet name="2" sheetId="2" r:id="rId2"/>
+    <sheet name="3" sheetId="3" r:id="rId3"/>
+    <sheet name="4" sheetId="4" r:id="rId4"/>
+    <sheet name="5" sheetId="5" r:id="rId5"/>
+    <sheet name="6" sheetId="6" r:id="rId6"/>
+    <sheet name="8" sheetId="7" r:id="rId7"/>
+    <sheet name="9" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -76,17 +76,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>فرم شماره 1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <sz val="7.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
@@ -391,17 +380,6 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t>رئيس کميسيون دائمی هيات امنا: مهدی کشميری</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
       <t>رئيس دستگاه اجرایی:   رضا قنبری</t>
     </r>
   </si>
@@ -3299,6 +3277,12 @@
       </rPr>
       <t>توضيحات</t>
     </r>
+  </si>
+  <si>
+    <t>رئيس کميسيون دائمی هيات امنا: مهدی کشميری</t>
+  </si>
+  <si>
+    <t>فرم شماره 1</t>
   </si>
 </sst>
 </file>
@@ -3805,7 +3789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="333">
+  <cellXfs count="334">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -4082,6 +4066,150 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="30" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="30" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="30" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="19" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="19" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="13" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="13" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="13" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="8" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="8" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="8" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="8" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="8" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="8" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="8" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
     </xf>
@@ -4103,9 +4231,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
     </xf>
@@ -4118,82 +4243,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="13" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="13" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="13" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="8" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="8" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="8" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="8" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="8" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="8" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="8" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4271,36 +4342,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
@@ -4340,6 +4381,120 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="7" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="7" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="7" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="16" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="16" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="16" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
     </xf>
@@ -4382,119 +4537,146 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="20" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="16" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="16" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="16" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="7" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="7" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="7" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
@@ -4530,144 +4712,60 @@
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="12" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4679,105 +4777,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="5" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="3" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="2" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="19" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="19" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="4" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="31" readingOrder="2"/>
     </xf>
@@ -4787,23 +4786,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="31" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="30" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="30" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="30" readingOrder="2"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="6" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5125,11 +5112,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="92" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="94"/>
+      <c r="A1" s="140" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="142"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -5138,21 +5125,21 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="98" t="s">
+      <c r="L1" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="100" t="s">
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="147" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="101"/>
+      <c r="Q1" s="148"/>
     </row>
     <row r="2" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="95"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
+      <c r="A2" s="143"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="145"/>
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -5163,97 +5150,97 @@
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="102" t="s">
+      <c r="N2" s="149" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="103"/>
-      <c r="P2" s="104" t="s">
+      <c r="O2" s="150"/>
+      <c r="P2" s="333" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q2" s="151"/>
+    </row>
+    <row r="3" spans="1:17" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="105"/>
-    </row>
-    <row r="3" spans="1:17" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="106" t="s">
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="109" t="s">
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="112" t="s">
+      <c r="L3" s="132"/>
+      <c r="M3" s="132"/>
+      <c r="N3" s="132"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="113"/>
-      <c r="M3" s="113"/>
-      <c r="N3" s="113"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="115" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="116"/>
+      <c r="Q3" s="135"/>
     </row>
     <row r="4" spans="1:17" ht="56.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>14</v>
-      </c>
       <c r="H4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="J4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>14</v>
-      </c>
       <c r="M4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="O4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="118"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="137"/>
     </row>
     <row r="5" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>236418</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="11">
         <v>106497</v>
@@ -5268,7 +5255,7 @@
         <v>29370</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" s="11">
         <v>4288</v>
@@ -5283,7 +5270,7 @@
         <v>207048</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M5" s="11">
         <v>102209</v>
@@ -5294,17 +5281,17 @@
       <c r="O5" s="11">
         <v>120010</v>
       </c>
-      <c r="P5" s="119" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q5" s="120"/>
+      <c r="P5" s="138" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="139"/>
     </row>
     <row r="6" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
         <v>175522</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="13">
         <v>67067</v>
@@ -5319,7 +5306,7 @@
         <v>21070</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" s="13">
         <v>4288</v>
@@ -5334,7 +5321,7 @@
         <v>154452</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M6" s="13">
         <v>62779</v>
@@ -5346,10 +5333,10 @@
         <v>74536</v>
       </c>
       <c r="P6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q6" s="116" t="s">
         <v>17</v>
-      </c>
-      <c r="Q6" s="121" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5357,7 +5344,7 @@
         <v>10432</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="16">
         <v>3785</v>
@@ -5372,7 +5359,7 @@
         <v>1480</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" s="16">
         <v>2600</v>
@@ -5387,7 +5374,7 @@
         <v>8952</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M7" s="16">
         <v>1185</v>
@@ -5399,16 +5386,16 @@
         <v>1185</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q7" s="122"/>
+        <v>18</v>
+      </c>
+      <c r="Q7" s="117"/>
     </row>
     <row r="8" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
         <v>151590</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="16">
         <v>63282</v>
@@ -5423,7 +5410,7 @@
         <v>6090</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" s="16">
         <v>1688</v>
@@ -5438,7 +5425,7 @@
         <v>145500</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M8" s="16">
         <v>61594</v>
@@ -5450,19 +5437,19 @@
         <v>73351</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q8" s="122"/>
+        <v>19</v>
+      </c>
+      <c r="Q8" s="117"/>
     </row>
     <row r="9" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16">
         <v>13500</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="16">
         <v>1030</v>
@@ -5474,10 +5461,10 @@
         <v>13500</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I9" s="16">
         <v>1030</v>
@@ -5486,31 +5473,31 @@
         <v>3500</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q9" s="123"/>
+        <v>20</v>
+      </c>
+      <c r="Q9" s="118"/>
     </row>
     <row r="10" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>60896</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="13">
         <v>39430</v>
@@ -5525,22 +5512,22 @@
         <v>8300</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K10" s="13">
         <v>52596</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M10" s="13">
         <v>39430</v>
@@ -5552,10 +5539,10 @@
         <v>45474</v>
       </c>
       <c r="P10" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q10" s="121" t="s">
-        <v>22</v>
+        <v>16</v>
+      </c>
+      <c r="Q10" s="116" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5563,7 +5550,7 @@
         <v>4690</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="19">
         <v>357</v>
@@ -5575,25 +5562,25 @@
         <v>357</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K11" s="16">
         <v>4690</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M11" s="19">
         <v>357</v>
@@ -5605,16 +5592,16 @@
         <v>357</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q11" s="122"/>
+        <v>18</v>
+      </c>
+      <c r="Q11" s="117"/>
     </row>
     <row r="12" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16">
         <v>38800</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="16">
         <v>24410</v>
@@ -5626,25 +5613,25 @@
         <v>29100</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K12" s="16">
         <v>38800</v>
       </c>
       <c r="L12" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M12" s="16">
         <v>24410</v>
@@ -5656,16 +5643,16 @@
         <v>29100</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="122"/>
+        <v>19</v>
+      </c>
+      <c r="Q12" s="117"/>
     </row>
     <row r="13" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="16">
         <v>17406</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="16">
         <v>14663</v>
@@ -5680,22 +5667,22 @@
         <v>8300</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K13" s="16">
         <v>9106</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M13" s="16">
         <v>14663</v>
@@ -5707,16 +5694,16 @@
         <v>16017</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" s="123"/>
+        <v>20</v>
+      </c>
+      <c r="Q13" s="118"/>
     </row>
     <row r="14" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="20">
         <v>105813</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="20">
         <v>16115</v>
@@ -5731,7 +5718,7 @@
         <v>24600</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H14" s="20">
         <v>4666</v>
@@ -5746,7 +5733,7 @@
         <v>81213</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M14" s="20">
         <v>11449</v>
@@ -5758,10 +5745,10 @@
         <v>21688</v>
       </c>
       <c r="P14" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q14" s="121" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="Q14" s="116" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -5769,7 +5756,7 @@
         <v>22239</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="16">
         <v>4856</v>
@@ -5784,7 +5771,7 @@
         <v>12000</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" s="16">
         <v>4066</v>
@@ -5799,7 +5786,7 @@
         <v>10239</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M15" s="19">
         <v>790</v>
@@ -5811,16 +5798,16 @@
         <v>3323</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q15" s="122"/>
+        <v>18</v>
+      </c>
+      <c r="Q15" s="117"/>
     </row>
     <row r="16" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="16">
         <v>52914</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="16">
         <v>11259</v>
@@ -5835,7 +5822,7 @@
         <v>12600</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" s="19">
         <v>600</v>
@@ -5850,7 +5837,7 @@
         <v>40314</v>
       </c>
       <c r="L16" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M16" s="16">
         <v>10659</v>
@@ -5862,111 +5849,121 @@
         <v>18365</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q16" s="122"/>
+        <v>23</v>
+      </c>
+      <c r="Q16" s="117"/>
     </row>
     <row r="17" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="16">
         <v>30660</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K17" s="16">
         <v>30660</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M17" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="118"/>
+    </row>
+    <row r="18" spans="1:17" ht="147.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="Q17" s="123"/>
-    </row>
-    <row r="18" spans="1:17" ht="147.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="124" t="s">
+      <c r="B18" s="120"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="120"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="120"/>
+      <c r="O18" s="120"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="125"/>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="125"/>
-      <c r="H18" s="125"/>
-      <c r="I18" s="125"/>
-      <c r="J18" s="125"/>
-      <c r="K18" s="125"/>
-      <c r="L18" s="125"/>
-      <c r="M18" s="125"/>
-      <c r="N18" s="125"/>
-      <c r="O18" s="125"/>
-      <c r="P18" s="126"/>
-      <c r="Q18" s="23" t="s">
+    </row>
+    <row r="19" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="122" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="127" t="s">
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="332" t="s">
+        <v>259</v>
+      </c>
+      <c r="F19" s="123"/>
+      <c r="G19" s="123"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="124"/>
+      <c r="L19" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="128"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="129"/>
-      <c r="E19" s="127" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="128"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="128"/>
-      <c r="I19" s="128"/>
-      <c r="J19" s="128"/>
-      <c r="K19" s="129"/>
-      <c r="L19" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="M19" s="128"/>
-      <c r="N19" s="128"/>
-      <c r="O19" s="128"/>
-      <c r="P19" s="128"/>
-      <c r="Q19" s="129"/>
+      <c r="M19" s="123"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="123"/>
+      <c r="P19" s="123"/>
+      <c r="Q19" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="P3:Q4"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="Q6:Q9"/>
     <mergeCell ref="Q10:Q13"/>
     <mergeCell ref="Q14:Q17"/>
@@ -5974,16 +5971,6 @@
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="E19:K19"/>
     <mergeCell ref="L19:Q19"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:O3"/>
-    <mergeCell ref="P3:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="L1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6000,123 +5987,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="130" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="132"/>
+      <c r="A1" s="159" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="160"/>
+      <c r="C1" s="161"/>
       <c r="D1" s="24"/>
       <c r="E1" s="25"/>
       <c r="F1" s="25"/>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
-      <c r="I1" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="136"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="138" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="137"/>
+      <c r="I1" s="165" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="165"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="167" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="166"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="133"/>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
+      <c r="A2" s="162"/>
+      <c r="B2" s="163"/>
+      <c r="C2" s="164"/>
       <c r="D2" s="26"/>
       <c r="E2" s="27"/>
       <c r="F2" s="27"/>
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
       <c r="I2" s="27"/>
-      <c r="J2" s="139" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="140"/>
+      <c r="J2" s="168" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="169"/>
       <c r="L2" s="26"/>
       <c r="M2" s="28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="170" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="125" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="141" t="s">
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="125" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="106" t="s">
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="173" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="106" t="s">
+      <c r="M3" s="176" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="144" t="s">
+    </row>
+    <row r="4" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="171"/>
+      <c r="B4" s="179" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="147" t="s">
+      <c r="C4" s="180"/>
+      <c r="D4" s="180"/>
+      <c r="E4" s="181"/>
+      <c r="F4" s="182" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="142"/>
-      <c r="B4" s="150" t="s">
+      <c r="G4" s="179" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="180"/>
+      <c r="I4" s="180"/>
+      <c r="J4" s="181"/>
+      <c r="K4" s="182" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="174"/>
+      <c r="M4" s="177"/>
+    </row>
+    <row r="5" spans="1:13" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="172"/>
+      <c r="B5" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="151"/>
-      <c r="D4" s="151"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="153" t="s">
+      <c r="C5" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="150" t="s">
+      <c r="D5" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="183"/>
+      <c r="G5" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="151"/>
-      <c r="I4" s="151"/>
-      <c r="J4" s="152"/>
-      <c r="K4" s="153" t="s">
+      <c r="H5" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="145"/>
-      <c r="M4" s="148"/>
-    </row>
-    <row r="5" spans="1:13" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="143"/>
-      <c r="B5" s="30" t="s">
+      <c r="I5" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="J5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="154"/>
-      <c r="G5" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="154"/>
-      <c r="L5" s="146"/>
-      <c r="M5" s="149"/>
+      <c r="K5" s="183"/>
+      <c r="L5" s="175"/>
+      <c r="M5" s="178"/>
     </row>
     <row r="6" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="31">
@@ -6152,10 +6139,10 @@
       <c r="K6" s="31">
         <v>67067</v>
       </c>
-      <c r="L6" s="155" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" s="156"/>
+      <c r="L6" s="152" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" s="153"/>
     </row>
     <row r="7" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="31">
@@ -6180,7 +6167,7 @@
         <v>154452</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I7" s="32">
         <v>145500</v>
@@ -6191,47 +6178,47 @@
       <c r="K7" s="32">
         <v>62779</v>
       </c>
-      <c r="L7" s="157" t="s">
-        <v>49</v>
-      </c>
-      <c r="M7" s="158"/>
+      <c r="L7" s="154" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="155"/>
     </row>
     <row r="8" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F8" s="36">
         <v>357</v>
       </c>
       <c r="G8" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="M8" s="37">
         <v>1804011000</v>
@@ -6245,22 +6232,22 @@
         <v>7627</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D9" s="38">
         <v>7627</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G9" s="32">
         <v>43164</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I9" s="38">
         <v>41046</v>
@@ -6272,7 +6259,7 @@
         <v>14887</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M9" s="37">
         <v>1804014000</v>
@@ -6292,7 +6279,7 @@
         <v>17455</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F10" s="38">
         <v>1750</v>
@@ -6301,7 +6288,7 @@
         <v>52514</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I10" s="38">
         <v>49470</v>
@@ -6313,7 +6300,7 @@
         <v>40249</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M10" s="37">
         <v>1805005000</v>
@@ -6327,7 +6314,7 @@
         <v>18408</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" s="38">
         <v>13718</v>
@@ -6342,7 +6329,7 @@
         <v>58774</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I11" s="38">
         <v>54984</v>
@@ -6354,7 +6341,7 @@
         <v>7643</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M11" s="37">
         <v>1805012000</v>
@@ -6362,222 +6349,222 @@
     </row>
     <row r="12" spans="1:13" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G12" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I12" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K12" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L12" s="39"/>
       <c r="M12" s="39"/>
     </row>
     <row r="13" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I13" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K13" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L13" s="39"/>
       <c r="M13" s="39"/>
     </row>
     <row r="14" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I14" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K14" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L14" s="39"/>
       <c r="M14" s="39"/>
     </row>
     <row r="15" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G15" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I15" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K15" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L15" s="39"/>
       <c r="M15" s="39"/>
     </row>
     <row r="16" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I16" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K16" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L16" s="39"/>
       <c r="M16" s="39"/>
     </row>
     <row r="17" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H17" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I17" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J17" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K17" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L17" s="39"/>
       <c r="M17" s="39"/>
@@ -6593,13 +6580,13 @@
         <v>8300</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G18" s="32">
         <v>21070</v>
@@ -6616,47 +6603,47 @@
       <c r="K18" s="32">
         <v>4288</v>
       </c>
-      <c r="L18" s="157" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="158"/>
+      <c r="L18" s="154" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="155"/>
     </row>
     <row r="19" spans="1:13" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H19" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I19" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J19" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K19" s="38">
         <v>2600</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M19" s="37">
         <v>1804010000</v>
@@ -6673,13 +6660,13 @@
         <v>8300</v>
       </c>
       <c r="D20" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F20" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G20" s="32">
         <v>21070</v>
@@ -6697,7 +6684,7 @@
         <v>1688</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M20" s="37">
         <v>1804011029</v>
@@ -6705,344 +6692,338 @@
     </row>
     <row r="21" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F21" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G21" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H21" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I21" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J21" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K21" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L21" s="39"/>
       <c r="M21" s="39"/>
     </row>
     <row r="22" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G22" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H22" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I22" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J22" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K22" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L22" s="39"/>
       <c r="M22" s="39"/>
     </row>
     <row r="23" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G23" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H23" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I23" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J23" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K23" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L23" s="39"/>
       <c r="M23" s="39"/>
     </row>
     <row r="24" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F24" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G24" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I24" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J24" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K24" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L24" s="39"/>
       <c r="M24" s="39"/>
     </row>
     <row r="25" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F25" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H25" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I25" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J25" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K25" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
     <row r="26" spans="1:13" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F26" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G26" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I26" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J26" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K26" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L26" s="39"/>
       <c r="M26" s="39"/>
     </row>
     <row r="27" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F27" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G27" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I27" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J27" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K27" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L27" s="39"/>
       <c r="M27" s="39"/>
     </row>
     <row r="28" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F28" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G28" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I28" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K28" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L28" s="39"/>
       <c r="M28" s="39"/>
     </row>
     <row r="29" spans="1:13" ht="51.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="159"/>
-      <c r="B29" s="160"/>
-      <c r="C29" s="160"/>
-      <c r="D29" s="160"/>
-      <c r="E29" s="160"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="160"/>
-      <c r="I29" s="160"/>
-      <c r="J29" s="160"/>
-      <c r="K29" s="160"/>
-      <c r="L29" s="161"/>
+      <c r="A29" s="95"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="96"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="96"/>
+      <c r="L29" s="97"/>
       <c r="M29" s="40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="156" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" s="157"/>
+      <c r="C30" s="157"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="157"/>
+      <c r="F30" s="157"/>
+      <c r="G30" s="157"/>
+      <c r="H30" s="157"/>
+      <c r="I30" s="158"/>
+      <c r="J30" s="156" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="162" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="163"/>
-      <c r="C30" s="163"/>
-      <c r="D30" s="163"/>
-      <c r="E30" s="163"/>
-      <c r="F30" s="163"/>
-      <c r="G30" s="163"/>
-      <c r="H30" s="163"/>
-      <c r="I30" s="164"/>
-      <c r="J30" s="162" t="s">
-        <v>59</v>
-      </c>
-      <c r="K30" s="163"/>
-      <c r="L30" s="163"/>
-      <c r="M30" s="164"/>
+      <c r="K30" s="157"/>
+      <c r="L30" s="157"/>
+      <c r="M30" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="J30:M30"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="L1:M1"/>
@@ -7056,6 +7037,12 @@
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="J30:M30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7072,57 +7059,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="166"/>
+      <c r="A1" s="184" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="185"/>
       <c r="C1" s="41" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="26"/>
       <c r="B2" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="186" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="43" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="167" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="168"/>
-      <c r="C3" s="169"/>
+      <c r="B3" s="187"/>
+      <c r="C3" s="188"/>
     </row>
     <row r="4" spans="1:3" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="408.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="170" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="171"/>
-      <c r="C5" s="172"/>
+      <c r="A5" s="189" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="190"/>
+      <c r="C5" s="191"/>
     </row>
     <row r="6" spans="1:3" ht="122.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="173"/>
-      <c r="B6" s="174"/>
-      <c r="C6" s="175"/>
+      <c r="A6" s="192"/>
+      <c r="B6" s="193"/>
+      <c r="C6" s="194"/>
     </row>
     <row r="7" spans="1:3" ht="30.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="176" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="177"/>
+        <v>65</v>
+      </c>
+      <c r="B7" s="195" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="196"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7151,10 +7138,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="178" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="179"/>
+      <c r="A1" s="235" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="236"/>
       <c r="C1" s="24"/>
       <c r="D1" s="25"/>
       <c r="E1" s="25"/>
@@ -7165,22 +7152,22 @@
       <c r="J1" s="25"/>
       <c r="K1" s="25"/>
       <c r="L1" s="25"/>
-      <c r="M1" s="182" t="s">
-        <v>70</v>
-      </c>
-      <c r="N1" s="182"/>
-      <c r="O1" s="182"/>
-      <c r="P1" s="182"/>
-      <c r="Q1" s="182"/>
-      <c r="R1" s="183"/>
+      <c r="M1" s="239" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="239"/>
+      <c r="O1" s="239"/>
+      <c r="P1" s="239"/>
+      <c r="Q1" s="239"/>
+      <c r="R1" s="240"/>
       <c r="S1" s="24"/>
       <c r="T1" s="46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="180"/>
-      <c r="B2" s="181"/>
+      <c r="A2" s="237"/>
+      <c r="B2" s="238"/>
       <c r="C2" s="26"/>
       <c r="D2" s="27"/>
       <c r="E2" s="27"/>
@@ -7194,153 +7181,153 @@
       <c r="M2" s="27"/>
       <c r="N2" s="27"/>
       <c r="O2" s="27"/>
-      <c r="P2" s="184" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q2" s="184"/>
-      <c r="R2" s="185"/>
+      <c r="P2" s="241" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q2" s="241"/>
+      <c r="R2" s="242"/>
       <c r="S2" s="26"/>
       <c r="T2" s="47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="243" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="244"/>
+      <c r="C3" s="244"/>
+      <c r="D3" s="244"/>
+      <c r="E3" s="244"/>
+      <c r="F3" s="244"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="244"/>
+      <c r="I3" s="244"/>
+      <c r="J3" s="244"/>
+      <c r="K3" s="244"/>
+      <c r="L3" s="245"/>
+      <c r="M3" s="246" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="186" t="s">
+      <c r="N3" s="247"/>
+      <c r="O3" s="247"/>
+      <c r="P3" s="247"/>
+      <c r="Q3" s="247"/>
+      <c r="R3" s="247"/>
+      <c r="S3" s="247"/>
+      <c r="T3" s="248"/>
+    </row>
+    <row r="4" spans="1:20" ht="15.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="209" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="187"/>
-      <c r="C3" s="187"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="187"/>
-      <c r="F3" s="187"/>
-      <c r="G3" s="187"/>
-      <c r="H3" s="187"/>
-      <c r="I3" s="187"/>
-      <c r="J3" s="187"/>
-      <c r="K3" s="187"/>
-      <c r="L3" s="188"/>
-      <c r="M3" s="189" t="s">
+      <c r="B4" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="N3" s="190"/>
-      <c r="O3" s="190"/>
-      <c r="P3" s="190"/>
-      <c r="Q3" s="190"/>
-      <c r="R3" s="190"/>
-      <c r="S3" s="190"/>
-      <c r="T3" s="191"/>
-    </row>
-    <row r="4" spans="1:20" ht="15.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="192" t="s">
+      <c r="C4" s="226" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="195" t="s">
+      <c r="D4" s="227"/>
+      <c r="E4" s="227"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="227"/>
+      <c r="H4" s="227"/>
+      <c r="I4" s="227"/>
+      <c r="J4" s="228"/>
+      <c r="K4" s="229" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="198" t="s">
+      <c r="L4" s="232" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="199"/>
-      <c r="E4" s="199"/>
-      <c r="F4" s="199"/>
-      <c r="G4" s="199"/>
-      <c r="H4" s="199"/>
-      <c r="I4" s="199"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="201" t="s">
+      <c r="M4" s="209" t="s">
         <v>79</v>
       </c>
-      <c r="L4" s="204" t="s">
+      <c r="N4" s="209" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="192" t="s">
+      <c r="O4" s="222" t="s">
         <v>81</v>
       </c>
-      <c r="N4" s="192" t="s">
+      <c r="P4" s="222" t="s">
         <v>82</v>
       </c>
-      <c r="O4" s="195" t="s">
+      <c r="Q4" s="215" t="s">
         <v>83</v>
       </c>
-      <c r="P4" s="195" t="s">
+      <c r="R4" s="209" t="s">
         <v>84</v>
       </c>
-      <c r="Q4" s="207" t="s">
+      <c r="S4" s="209" t="s">
         <v>85</v>
       </c>
-      <c r="R4" s="192" t="s">
+      <c r="T4" s="212" t="s">
         <v>86</v>
       </c>
-      <c r="S4" s="192" t="s">
+    </row>
+    <row r="5" spans="1:20" ht="15.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="210"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="215" t="s">
         <v>87</v>
       </c>
-      <c r="T4" s="210" t="s">
+      <c r="D5" s="217" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="15.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="193"/>
-      <c r="B5" s="196"/>
-      <c r="C5" s="207" t="s">
+      <c r="E5" s="219" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="213" t="s">
+      <c r="F5" s="220"/>
+      <c r="G5" s="221"/>
+      <c r="H5" s="219" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="215" t="s">
+      <c r="I5" s="220"/>
+      <c r="J5" s="221"/>
+      <c r="K5" s="230"/>
+      <c r="L5" s="233"/>
+      <c r="M5" s="210"/>
+      <c r="N5" s="210"/>
+      <c r="O5" s="223"/>
+      <c r="P5" s="223"/>
+      <c r="Q5" s="225"/>
+      <c r="R5" s="210"/>
+      <c r="S5" s="210"/>
+      <c r="T5" s="213"/>
+    </row>
+    <row r="6" spans="1:20" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="211"/>
+      <c r="B6" s="224"/>
+      <c r="C6" s="216"/>
+      <c r="D6" s="218"/>
+      <c r="E6" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="216"/>
-      <c r="G5" s="217"/>
-      <c r="H5" s="215" t="s">
+      <c r="F6" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="I5" s="216"/>
-      <c r="J5" s="217"/>
-      <c r="K5" s="202"/>
-      <c r="L5" s="205"/>
-      <c r="M5" s="193"/>
-      <c r="N5" s="193"/>
-      <c r="O5" s="196"/>
-      <c r="P5" s="196"/>
-      <c r="Q5" s="208"/>
-      <c r="R5" s="193"/>
-      <c r="S5" s="193"/>
-      <c r="T5" s="211"/>
-    </row>
-    <row r="6" spans="1:20" ht="33.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="194"/>
-      <c r="B6" s="197"/>
-      <c r="C6" s="209"/>
-      <c r="D6" s="214"/>
-      <c r="E6" s="48" t="s">
+      <c r="G6" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="H6" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="I6" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="J6" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="K6" s="203"/>
-      <c r="L6" s="206"/>
-      <c r="M6" s="194"/>
-      <c r="N6" s="194"/>
-      <c r="O6" s="197"/>
-      <c r="P6" s="197"/>
-      <c r="Q6" s="209"/>
-      <c r="R6" s="194"/>
-      <c r="S6" s="194"/>
-      <c r="T6" s="212"/>
+      <c r="K6" s="231"/>
+      <c r="L6" s="234"/>
+      <c r="M6" s="211"/>
+      <c r="N6" s="211"/>
+      <c r="O6" s="224"/>
+      <c r="P6" s="224"/>
+      <c r="Q6" s="216"/>
+      <c r="R6" s="211"/>
+      <c r="S6" s="211"/>
+      <c r="T6" s="214"/>
     </row>
     <row r="7" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="52">
@@ -7379,16 +7366,16 @@
       <c r="L7" s="52">
         <v>148070</v>
       </c>
-      <c r="M7" s="218" t="s">
-        <v>97</v>
-      </c>
-      <c r="N7" s="219"/>
-      <c r="O7" s="219"/>
-      <c r="P7" s="219"/>
-      <c r="Q7" s="219"/>
-      <c r="R7" s="219"/>
-      <c r="S7" s="219"/>
-      <c r="T7" s="220"/>
+      <c r="M7" s="200" t="s">
+        <v>95</v>
+      </c>
+      <c r="N7" s="201"/>
+      <c r="O7" s="201"/>
+      <c r="P7" s="201"/>
+      <c r="Q7" s="201"/>
+      <c r="R7" s="201"/>
+      <c r="S7" s="201"/>
+      <c r="T7" s="202"/>
     </row>
     <row r="8" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="52">
@@ -7427,16 +7414,16 @@
       <c r="L8" s="55">
         <v>106133</v>
       </c>
-      <c r="M8" s="221" t="s">
-        <v>98</v>
-      </c>
-      <c r="N8" s="222"/>
-      <c r="O8" s="222"/>
-      <c r="P8" s="222"/>
-      <c r="Q8" s="222"/>
-      <c r="R8" s="222"/>
-      <c r="S8" s="222"/>
-      <c r="T8" s="223"/>
+      <c r="M8" s="203" t="s">
+        <v>96</v>
+      </c>
+      <c r="N8" s="204"/>
+      <c r="O8" s="204"/>
+      <c r="P8" s="204"/>
+      <c r="Q8" s="204"/>
+      <c r="R8" s="204"/>
+      <c r="S8" s="204"/>
+      <c r="T8" s="205"/>
     </row>
     <row r="9" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="52">
@@ -7491,13 +7478,13 @@
         <v>15.2</v>
       </c>
       <c r="R9" s="59" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="S9" s="56">
         <v>6183</v>
       </c>
       <c r="T9" s="59" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7553,13 +7540,13 @@
         <v>0.2</v>
       </c>
       <c r="R10" s="59" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="S10" s="56">
         <v>1870</v>
       </c>
       <c r="T10" s="59" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7615,13 +7602,13 @@
         <v>13.6</v>
       </c>
       <c r="R11" s="59" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="S11" s="56">
         <v>2000</v>
       </c>
       <c r="T11" s="59" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7677,13 +7664,13 @@
         <v>6.9</v>
       </c>
       <c r="R12" s="59" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="S12" s="56">
         <v>2000</v>
       </c>
       <c r="T12" s="59" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7843,26 +7830,26 @@
       <c r="T18" s="60"/>
     </row>
     <row r="19" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="224"/>
-      <c r="B19" s="225"/>
-      <c r="C19" s="225"/>
-      <c r="D19" s="225"/>
-      <c r="E19" s="225"/>
-      <c r="F19" s="225"/>
-      <c r="G19" s="225"/>
-      <c r="H19" s="225"/>
-      <c r="I19" s="225"/>
-      <c r="J19" s="225"/>
-      <c r="K19" s="225"/>
-      <c r="L19" s="225"/>
-      <c r="M19" s="225"/>
-      <c r="N19" s="225"/>
-      <c r="O19" s="225"/>
-      <c r="P19" s="225"/>
-      <c r="Q19" s="225"/>
-      <c r="R19" s="225"/>
-      <c r="S19" s="225"/>
-      <c r="T19" s="226"/>
+      <c r="A19" s="206"/>
+      <c r="B19" s="207"/>
+      <c r="C19" s="207"/>
+      <c r="D19" s="207"/>
+      <c r="E19" s="207"/>
+      <c r="F19" s="207"/>
+      <c r="G19" s="207"/>
+      <c r="H19" s="207"/>
+      <c r="I19" s="207"/>
+      <c r="J19" s="207"/>
+      <c r="K19" s="207"/>
+      <c r="L19" s="207"/>
+      <c r="M19" s="207"/>
+      <c r="N19" s="207"/>
+      <c r="O19" s="207"/>
+      <c r="P19" s="207"/>
+      <c r="Q19" s="207"/>
+      <c r="R19" s="207"/>
+      <c r="S19" s="207"/>
+      <c r="T19" s="208"/>
     </row>
     <row r="20" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="52">
@@ -7901,16 +7888,16 @@
       <c r="L20" s="55">
         <v>41937</v>
       </c>
-      <c r="M20" s="221" t="s">
-        <v>104</v>
-      </c>
-      <c r="N20" s="222"/>
-      <c r="O20" s="222"/>
-      <c r="P20" s="222"/>
-      <c r="Q20" s="222"/>
-      <c r="R20" s="222"/>
-      <c r="S20" s="222"/>
-      <c r="T20" s="223"/>
+      <c r="M20" s="203" t="s">
+        <v>102</v>
+      </c>
+      <c r="N20" s="204"/>
+      <c r="O20" s="204"/>
+      <c r="P20" s="204"/>
+      <c r="Q20" s="204"/>
+      <c r="R20" s="204"/>
+      <c r="S20" s="204"/>
+      <c r="T20" s="205"/>
     </row>
     <row r="21" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="53">
@@ -7965,13 +7952,13 @@
         <v>156.9</v>
       </c>
       <c r="R21" s="59" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="S21" s="56">
         <v>1</v>
       </c>
       <c r="T21" s="59" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8027,13 +8014,13 @@
         <v>27476</v>
       </c>
       <c r="R22" s="59" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="S22" s="56">
         <v>1</v>
       </c>
       <c r="T22" s="59" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8089,13 +8076,13 @@
         <v>40074</v>
       </c>
       <c r="R23" s="59" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="S23" s="56">
         <v>1</v>
       </c>
       <c r="T23" s="59" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8151,13 +8138,13 @@
         <v>7695</v>
       </c>
       <c r="R24" s="59" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="S24" s="56">
         <v>1</v>
       </c>
       <c r="T24" s="59" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8351,66 +8338,69 @@
       </c>
     </row>
     <row r="31" spans="1:20" ht="84.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="124" t="s">
+      <c r="A31" s="119" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="120"/>
+      <c r="C31" s="120"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="120"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="120"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="120"/>
+      <c r="O31" s="120"/>
+      <c r="P31" s="120"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="120"/>
+      <c r="S31" s="121"/>
+      <c r="T31" s="62" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="23.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="197" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="125"/>
-      <c r="C31" s="125"/>
-      <c r="D31" s="125"/>
-      <c r="E31" s="125"/>
-      <c r="F31" s="125"/>
-      <c r="G31" s="125"/>
-      <c r="H31" s="125"/>
-      <c r="I31" s="125"/>
-      <c r="J31" s="125"/>
-      <c r="K31" s="125"/>
-      <c r="L31" s="125"/>
-      <c r="M31" s="125"/>
-      <c r="N31" s="125"/>
-      <c r="O31" s="125"/>
-      <c r="P31" s="125"/>
-      <c r="Q31" s="125"/>
-      <c r="R31" s="125"/>
-      <c r="S31" s="126"/>
-      <c r="T31" s="62" t="s">
+      <c r="B32" s="198"/>
+      <c r="C32" s="198"/>
+      <c r="D32" s="198"/>
+      <c r="E32" s="198"/>
+      <c r="F32" s="198"/>
+      <c r="G32" s="198"/>
+      <c r="H32" s="198"/>
+      <c r="I32" s="198"/>
+      <c r="J32" s="198"/>
+      <c r="K32" s="198"/>
+      <c r="L32" s="199"/>
+      <c r="M32" s="197" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" ht="23.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="227" t="s">
-        <v>112</v>
-      </c>
-      <c r="B32" s="228"/>
-      <c r="C32" s="228"/>
-      <c r="D32" s="228"/>
-      <c r="E32" s="228"/>
-      <c r="F32" s="228"/>
-      <c r="G32" s="228"/>
-      <c r="H32" s="228"/>
-      <c r="I32" s="228"/>
-      <c r="J32" s="228"/>
-      <c r="K32" s="228"/>
-      <c r="L32" s="229"/>
-      <c r="M32" s="227" t="s">
-        <v>113</v>
-      </c>
-      <c r="N32" s="228"/>
-      <c r="O32" s="228"/>
-      <c r="P32" s="228"/>
-      <c r="Q32" s="228"/>
-      <c r="R32" s="228"/>
-      <c r="S32" s="228"/>
-      <c r="T32" s="229"/>
+      <c r="N32" s="198"/>
+      <c r="O32" s="198"/>
+      <c r="P32" s="198"/>
+      <c r="Q32" s="198"/>
+      <c r="R32" s="198"/>
+      <c r="S32" s="198"/>
+      <c r="T32" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="M32:T32"/>
-    <mergeCell ref="M7:T7"/>
-    <mergeCell ref="M8:T8"/>
-    <mergeCell ref="A19:T19"/>
-    <mergeCell ref="M20:T20"/>
-    <mergeCell ref="A31:S31"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="M3:T3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="L4:L6"/>
     <mergeCell ref="R4:R6"/>
     <mergeCell ref="S4:S6"/>
     <mergeCell ref="T4:T6"/>
@@ -8423,16 +8413,13 @@
     <mergeCell ref="O4:O6"/>
     <mergeCell ref="P4:P6"/>
     <mergeCell ref="Q4:Q6"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="K4:K6"/>
-    <mergeCell ref="L4:L6"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="M1:R1"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="M3:T3"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="M32:T32"/>
+    <mergeCell ref="M7:T7"/>
+    <mergeCell ref="M8:T8"/>
+    <mergeCell ref="A19:T19"/>
+    <mergeCell ref="M20:T20"/>
+    <mergeCell ref="A31:S31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8454,102 +8441,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="230" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="231"/>
+      <c r="A1" s="296" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="297"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="234" t="s">
-        <v>114</v>
-      </c>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="236" t="s">
-        <v>115</v>
-      </c>
-      <c r="L1" s="234"/>
-      <c r="M1" s="235"/>
+      <c r="G1" s="300" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="300"/>
+      <c r="I1" s="300"/>
+      <c r="J1" s="301"/>
+      <c r="K1" s="302" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" s="300"/>
+      <c r="M1" s="301"/>
     </row>
     <row r="2" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="232"/>
-      <c r="B2" s="233"/>
+      <c r="A2" s="298"/>
+      <c r="B2" s="299"/>
       <c r="C2" s="4"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="237" t="s">
+      <c r="I2" s="303" t="s">
+        <v>114</v>
+      </c>
+      <c r="J2" s="304"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="305" t="s">
+        <v>115</v>
+      </c>
+      <c r="M2" s="306"/>
+    </row>
+    <row r="3" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="286" t="s">
         <v>116</v>
       </c>
-      <c r="J2" s="238"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="239" t="s">
+      <c r="B3" s="287"/>
+      <c r="C3" s="288" t="s">
         <v>117</v>
       </c>
-      <c r="M2" s="240"/>
-    </row>
-    <row r="3" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="241" t="s">
+      <c r="D3" s="268" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="242"/>
-      <c r="C3" s="243" t="s">
+      <c r="E3" s="290" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="245" t="s">
+      <c r="F3" s="291"/>
+      <c r="G3" s="292"/>
+      <c r="H3" s="293" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="247" t="s">
+      <c r="I3" s="294"/>
+      <c r="J3" s="295"/>
+      <c r="K3" s="274" t="s">
         <v>121</v>
       </c>
-      <c r="F3" s="248"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="250" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="251"/>
-      <c r="J3" s="252"/>
-      <c r="K3" s="253" t="s">
-        <v>123</v>
-      </c>
-      <c r="L3" s="254"/>
-      <c r="M3" s="255"/>
+      <c r="L3" s="275"/>
+      <c r="M3" s="276"/>
     </row>
     <row r="4" spans="1:13" ht="22.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="65" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="289"/>
+      <c r="D4" s="270"/>
+      <c r="E4" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="F4" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="244"/>
-      <c r="D4" s="246"/>
-      <c r="E4" s="64" t="s">
+      <c r="G4" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="66" t="s">
-        <v>127</v>
-      </c>
-      <c r="G4" s="66" t="s">
-        <v>128</v>
-      </c>
       <c r="H4" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="I4" s="66" t="s">
+        <v>125</v>
+      </c>
+      <c r="J4" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="I4" s="66" t="s">
-        <v>127</v>
-      </c>
-      <c r="J4" s="66" t="s">
-        <v>128</v>
-      </c>
-      <c r="K4" s="256"/>
-      <c r="L4" s="257"/>
-      <c r="M4" s="258"/>
+      <c r="K4" s="277"/>
+      <c r="L4" s="278"/>
+      <c r="M4" s="279"/>
     </row>
     <row r="5" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="67">
@@ -8582,11 +8569,11 @@
       <c r="J5" s="67">
         <v>62779</v>
       </c>
-      <c r="K5" s="259" t="s">
-        <v>126</v>
-      </c>
-      <c r="L5" s="260"/>
-      <c r="M5" s="261"/>
+      <c r="K5" s="280" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="281"/>
+      <c r="M5" s="282"/>
     </row>
     <row r="6" spans="1:13" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="69">
@@ -8619,11 +8606,11 @@
       <c r="J6" s="69">
         <v>30330</v>
       </c>
-      <c r="K6" s="262" t="s">
-        <v>129</v>
-      </c>
-      <c r="L6" s="263"/>
-      <c r="M6" s="264"/>
+      <c r="K6" s="283" t="s">
+        <v>127</v>
+      </c>
+      <c r="L6" s="284"/>
+      <c r="M6" s="285"/>
     </row>
     <row r="7" spans="1:13" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="72">
@@ -8657,10 +8644,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="66" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L7" s="265" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M7" s="74">
         <v>1</v>
@@ -8698,7 +8685,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="66" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L8" s="266"/>
       <c r="M8" s="74">
@@ -8737,7 +8724,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="66" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L9" s="266"/>
       <c r="M9" s="74">
@@ -8776,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="66" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L10" s="266"/>
       <c r="M10" s="74">
@@ -8794,7 +8781,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D11" s="75" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E11" s="72">
         <v>648</v>
@@ -8815,7 +8802,7 @@
         <v>1083</v>
       </c>
       <c r="K11" s="66" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L11" s="267"/>
       <c r="M11" s="74">
@@ -8854,13 +8841,13 @@
         <v>10014</v>
       </c>
       <c r="K12" s="66" t="s">
+        <v>135</v>
+      </c>
+      <c r="L12" s="268" t="s">
+        <v>136</v>
+      </c>
+      <c r="M12" s="77" t="s">
         <v>137</v>
-      </c>
-      <c r="L12" s="245" t="s">
-        <v>138</v>
-      </c>
-      <c r="M12" s="77" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -8895,9 +8882,9 @@
         <v>175</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="L13" s="268"/>
+        <v>138</v>
+      </c>
+      <c r="L13" s="269"/>
       <c r="M13" s="74">
         <v>7</v>
       </c>
@@ -8913,7 +8900,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="D14" s="75" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E14" s="72">
         <v>667</v>
@@ -8934,9 +8921,9 @@
         <v>636</v>
       </c>
       <c r="K14" s="66" t="s">
-        <v>142</v>
-      </c>
-      <c r="L14" s="268"/>
+        <v>140</v>
+      </c>
+      <c r="L14" s="269"/>
       <c r="M14" s="74">
         <v>8</v>
       </c>
@@ -8952,7 +8939,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="D15" s="75" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E15" s="76">
         <v>2752</v>
@@ -8973,9 +8960,9 @@
         <v>3264</v>
       </c>
       <c r="K15" s="66" t="s">
-        <v>144</v>
-      </c>
-      <c r="L15" s="246"/>
+        <v>142</v>
+      </c>
+      <c r="L15" s="270"/>
       <c r="M15" s="74">
         <v>9</v>
       </c>
@@ -9012,10 +8999,10 @@
         <v>12529</v>
       </c>
       <c r="K16" s="66" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L16" s="265" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M16" s="74">
         <v>10</v>
@@ -9053,7 +9040,7 @@
         <v>290</v>
       </c>
       <c r="K17" s="66" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L17" s="266"/>
       <c r="M17" s="74">
@@ -9092,7 +9079,7 @@
         <v>425</v>
       </c>
       <c r="K18" s="66" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L18" s="266"/>
       <c r="M18" s="74">
@@ -9131,7 +9118,7 @@
         <v>1834</v>
       </c>
       <c r="K19" s="66" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L19" s="267"/>
       <c r="M19" s="74">
@@ -9170,10 +9157,10 @@
         <v>0</v>
       </c>
       <c r="K20" s="66" t="s">
-        <v>150</v>
-      </c>
-      <c r="L20" s="245" t="s">
-        <v>151</v>
+        <v>148</v>
+      </c>
+      <c r="L20" s="268" t="s">
+        <v>149</v>
       </c>
       <c r="M20" s="74">
         <v>14</v>
@@ -9211,9 +9198,9 @@
         <v>0</v>
       </c>
       <c r="K21" s="66" t="s">
-        <v>152</v>
-      </c>
-      <c r="L21" s="246"/>
+        <v>150</v>
+      </c>
+      <c r="L21" s="270"/>
       <c r="M21" s="74">
         <v>15</v>
       </c>
@@ -9249,12 +9236,12 @@
       <c r="J22" s="72">
         <v>0</v>
       </c>
-      <c r="K22" s="269" t="s">
-        <v>153</v>
-      </c>
-      <c r="L22" s="270"/>
+      <c r="K22" s="254" t="s">
+        <v>151</v>
+      </c>
+      <c r="L22" s="255"/>
       <c r="M22" s="77" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -9288,10 +9275,10 @@
       <c r="J23" s="72">
         <v>80</v>
       </c>
-      <c r="K23" s="269" t="s">
-        <v>155</v>
-      </c>
-      <c r="L23" s="270"/>
+      <c r="K23" s="254" t="s">
+        <v>153</v>
+      </c>
+      <c r="L23" s="255"/>
       <c r="M23" s="74">
         <v>17</v>
       </c>
@@ -9327,10 +9314,10 @@
       <c r="J24" s="72">
         <v>0</v>
       </c>
-      <c r="K24" s="269" t="s">
-        <v>156</v>
-      </c>
-      <c r="L24" s="270"/>
+      <c r="K24" s="254" t="s">
+        <v>154</v>
+      </c>
+      <c r="L24" s="255"/>
       <c r="M24" s="74">
         <v>18</v>
       </c>
@@ -9366,10 +9353,10 @@
       <c r="J25" s="72">
         <v>0</v>
       </c>
-      <c r="K25" s="269" t="s">
-        <v>157</v>
-      </c>
-      <c r="L25" s="270"/>
+      <c r="K25" s="254" t="s">
+        <v>155</v>
+      </c>
+      <c r="L25" s="255"/>
       <c r="M25" s="74">
         <v>19</v>
       </c>
@@ -9405,11 +9392,11 @@
       <c r="J26" s="69">
         <v>4825</v>
       </c>
-      <c r="K26" s="271" t="s">
-        <v>158</v>
-      </c>
-      <c r="L26" s="272"/>
-      <c r="M26" s="273"/>
+      <c r="K26" s="262" t="s">
+        <v>156</v>
+      </c>
+      <c r="L26" s="263"/>
+      <c r="M26" s="264"/>
     </row>
     <row r="27" spans="1:13" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="72">
@@ -9443,10 +9430,10 @@
         <v>0</v>
       </c>
       <c r="K27" s="66" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="L27" s="265" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M27" s="74">
         <v>20</v>
@@ -9484,7 +9471,7 @@
         <v>350</v>
       </c>
       <c r="K28" s="66" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L28" s="266"/>
       <c r="M28" s="74">
@@ -9523,7 +9510,7 @@
         <v>1009</v>
       </c>
       <c r="K29" s="66" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L29" s="266"/>
       <c r="M29" s="74">
@@ -9562,7 +9549,7 @@
         <v>892</v>
       </c>
       <c r="K30" s="66" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="L30" s="267"/>
       <c r="M30" s="74">
@@ -9601,10 +9588,10 @@
         <v>593</v>
       </c>
       <c r="K31" s="78" t="s">
-        <v>164</v>
-      </c>
-      <c r="L31" s="245" t="s">
-        <v>165</v>
+        <v>162</v>
+      </c>
+      <c r="L31" s="268" t="s">
+        <v>163</v>
       </c>
       <c r="M31" s="74">
         <v>24</v>
@@ -9642,9 +9629,9 @@
         <v>519</v>
       </c>
       <c r="K32" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="L32" s="268"/>
+        <v>164</v>
+      </c>
+      <c r="L32" s="269"/>
       <c r="M32" s="74">
         <v>25</v>
       </c>
@@ -9681,11 +9668,11 @@
         <v>1462</v>
       </c>
       <c r="K33" s="78" t="s">
-        <v>167</v>
-      </c>
-      <c r="L33" s="268"/>
+        <v>165</v>
+      </c>
+      <c r="L33" s="269"/>
       <c r="M33" s="77" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -9699,7 +9686,7 @@
         <v>1E-3</v>
       </c>
       <c r="D34" s="75" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E34" s="72">
         <v>145</v>
@@ -9720,9 +9707,9 @@
         <v>0</v>
       </c>
       <c r="K34" s="66" t="s">
-        <v>170</v>
-      </c>
-      <c r="L34" s="246"/>
+        <v>168</v>
+      </c>
+      <c r="L34" s="270"/>
       <c r="M34" s="74">
         <v>27</v>
       </c>
@@ -9759,10 +9746,10 @@
         <v>0</v>
       </c>
       <c r="K35" s="66" t="s">
-        <v>171</v>
-      </c>
-      <c r="L35" s="274" t="s">
-        <v>172</v>
+        <v>169</v>
+      </c>
+      <c r="L35" s="271" t="s">
+        <v>170</v>
       </c>
       <c r="M35" s="74">
         <v>28</v>
@@ -9800,9 +9787,9 @@
         <v>0</v>
       </c>
       <c r="K36" s="66" t="s">
-        <v>173</v>
-      </c>
-      <c r="L36" s="275"/>
+        <v>171</v>
+      </c>
+      <c r="L36" s="272"/>
       <c r="M36" s="74">
         <v>29</v>
       </c>
@@ -9839,9 +9826,9 @@
         <v>0</v>
       </c>
       <c r="K37" s="66" t="s">
-        <v>174</v>
-      </c>
-      <c r="L37" s="275"/>
+        <v>172</v>
+      </c>
+      <c r="L37" s="272"/>
       <c r="M37" s="74">
         <v>30</v>
       </c>
@@ -9878,9 +9865,9 @@
         <v>0</v>
       </c>
       <c r="K38" s="66" t="s">
-        <v>175</v>
-      </c>
-      <c r="L38" s="276"/>
+        <v>173</v>
+      </c>
+      <c r="L38" s="273"/>
       <c r="M38" s="74">
         <v>31</v>
       </c>
@@ -9896,7 +9883,7 @@
         <v>0.253</v>
       </c>
       <c r="D39" s="79" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E39" s="69">
         <v>52290</v>
@@ -9916,11 +9903,11 @@
       <c r="J39" s="69">
         <v>27624</v>
       </c>
-      <c r="K39" s="277" t="s">
-        <v>177</v>
-      </c>
-      <c r="L39" s="278"/>
-      <c r="M39" s="279"/>
+      <c r="K39" s="256" t="s">
+        <v>175</v>
+      </c>
+      <c r="L39" s="257"/>
+      <c r="M39" s="258"/>
     </row>
     <row r="40" spans="1:13" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="72">
@@ -9953,10 +9940,10 @@
       <c r="J40" s="76">
         <v>2113</v>
       </c>
-      <c r="K40" s="269" t="s">
-        <v>178</v>
-      </c>
-      <c r="L40" s="270"/>
+      <c r="K40" s="254" t="s">
+        <v>176</v>
+      </c>
+      <c r="L40" s="255"/>
       <c r="M40" s="74">
         <v>32</v>
       </c>
@@ -9972,7 +9959,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="D41" s="75" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E41" s="76">
         <v>1898</v>
@@ -9993,10 +9980,10 @@
         <v>2201</v>
       </c>
       <c r="K41" s="66" t="s">
-        <v>180</v>
-      </c>
-      <c r="L41" s="280" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="L41" s="259" t="s">
+        <v>179</v>
       </c>
       <c r="M41" s="74">
         <v>33</v>
@@ -10034,9 +10021,9 @@
         <v>17740</v>
       </c>
       <c r="K42" s="66" t="s">
-        <v>182</v>
-      </c>
-      <c r="L42" s="281"/>
+        <v>180</v>
+      </c>
+      <c r="L42" s="260"/>
       <c r="M42" s="74">
         <v>34</v>
       </c>
@@ -10073,9 +10060,9 @@
         <v>79</v>
       </c>
       <c r="K43" s="66" t="s">
-        <v>183</v>
-      </c>
-      <c r="L43" s="281"/>
+        <v>181</v>
+      </c>
+      <c r="L43" s="260"/>
       <c r="M43" s="74">
         <v>35</v>
       </c>
@@ -10112,11 +10099,11 @@
         <v>2067</v>
       </c>
       <c r="K44" s="66" t="s">
-        <v>184</v>
-      </c>
-      <c r="L44" s="281"/>
+        <v>182</v>
+      </c>
+      <c r="L44" s="260"/>
       <c r="M44" s="77" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -10130,7 +10117,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D45" s="75" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E45" s="76">
         <v>1038</v>
@@ -10151,9 +10138,9 @@
         <v>460</v>
       </c>
       <c r="K45" s="66" t="s">
-        <v>187</v>
-      </c>
-      <c r="L45" s="282"/>
+        <v>185</v>
+      </c>
+      <c r="L45" s="261"/>
       <c r="M45" s="74">
         <v>37</v>
       </c>
@@ -10189,10 +10176,10 @@
       <c r="J46" s="72">
         <v>485</v>
       </c>
-      <c r="K46" s="269" t="s">
-        <v>188</v>
-      </c>
-      <c r="L46" s="270"/>
+      <c r="K46" s="254" t="s">
+        <v>186</v>
+      </c>
+      <c r="L46" s="255"/>
       <c r="M46" s="74">
         <v>38</v>
       </c>
@@ -10229,10 +10216,10 @@
         <v>992</v>
       </c>
       <c r="K47" s="66" t="s">
-        <v>189</v>
-      </c>
-      <c r="L47" s="280" t="s">
-        <v>190</v>
+        <v>187</v>
+      </c>
+      <c r="L47" s="259" t="s">
+        <v>188</v>
       </c>
       <c r="M47" s="74">
         <v>39</v>
@@ -10270,9 +10257,9 @@
         <v>330</v>
       </c>
       <c r="K48" s="66" t="s">
-        <v>191</v>
-      </c>
-      <c r="L48" s="281"/>
+        <v>189</v>
+      </c>
+      <c r="L48" s="260"/>
       <c r="M48" s="74">
         <v>40</v>
       </c>
@@ -10288,7 +10275,7 @@
         <v>2E-3</v>
       </c>
       <c r="D49" s="75" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E49" s="72">
         <v>500</v>
@@ -10309,9 +10296,9 @@
         <v>133</v>
       </c>
       <c r="K49" s="66" t="s">
-        <v>193</v>
-      </c>
-      <c r="L49" s="281"/>
+        <v>191</v>
+      </c>
+      <c r="L49" s="260"/>
       <c r="M49" s="74">
         <v>41</v>
       </c>
@@ -10348,9 +10335,9 @@
         <v>0</v>
       </c>
       <c r="K50" s="66" t="s">
-        <v>194</v>
-      </c>
-      <c r="L50" s="282"/>
+        <v>192</v>
+      </c>
+      <c r="L50" s="261"/>
       <c r="M50" s="74">
         <v>42</v>
       </c>
@@ -10387,10 +10374,10 @@
         <v>0</v>
       </c>
       <c r="K51" s="66" t="s">
-        <v>195</v>
-      </c>
-      <c r="L51" s="283" t="s">
-        <v>196</v>
+        <v>193</v>
+      </c>
+      <c r="L51" s="252" t="s">
+        <v>194</v>
       </c>
       <c r="M51" s="74">
         <v>43</v>
@@ -10428,9 +10415,9 @@
         <v>0</v>
       </c>
       <c r="K52" s="66" t="s">
-        <v>197</v>
-      </c>
-      <c r="L52" s="284"/>
+        <v>195</v>
+      </c>
+      <c r="L52" s="253"/>
       <c r="M52" s="74">
         <v>44</v>
       </c>
@@ -10466,10 +10453,10 @@
       <c r="J53" s="76">
         <v>1024</v>
       </c>
-      <c r="K53" s="124" t="s">
-        <v>198</v>
-      </c>
-      <c r="L53" s="126"/>
+      <c r="K53" s="119" t="s">
+        <v>196</v>
+      </c>
+      <c r="L53" s="121"/>
       <c r="M53" s="74">
         <v>45</v>
       </c>
@@ -10485,7 +10472,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="D54" s="75" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E54" s="76">
         <v>1850</v>
@@ -10505,12 +10492,12 @@
       <c r="J54" s="72">
         <v>0</v>
       </c>
-      <c r="K54" s="269" t="s">
-        <v>200</v>
-      </c>
-      <c r="L54" s="270"/>
+      <c r="K54" s="254" t="s">
+        <v>198</v>
+      </c>
+      <c r="L54" s="255"/>
       <c r="M54" s="77" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -10544,10 +10531,10 @@
       <c r="J55" s="72">
         <v>0</v>
       </c>
-      <c r="K55" s="269" t="s">
-        <v>202</v>
-      </c>
-      <c r="L55" s="270"/>
+      <c r="K55" s="254" t="s">
+        <v>200</v>
+      </c>
+      <c r="L55" s="255"/>
       <c r="M55" s="74">
         <v>47</v>
       </c>
@@ -10583,35 +10570,65 @@
       <c r="J56" s="72">
         <v>0</v>
       </c>
-      <c r="K56" s="269" t="s">
-        <v>203</v>
-      </c>
-      <c r="L56" s="270"/>
+      <c r="K56" s="254" t="s">
+        <v>201</v>
+      </c>
+      <c r="L56" s="255"/>
       <c r="M56" s="74">
         <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="285" t="s">
-        <v>204</v>
-      </c>
-      <c r="B57" s="286"/>
-      <c r="C57" s="286"/>
-      <c r="D57" s="286"/>
-      <c r="E57" s="286"/>
-      <c r="F57" s="286"/>
-      <c r="G57" s="286"/>
-      <c r="H57" s="286"/>
-      <c r="I57" s="286"/>
-      <c r="J57" s="287"/>
-      <c r="K57" s="285" t="s">
-        <v>205</v>
-      </c>
-      <c r="L57" s="286"/>
-      <c r="M57" s="287"/>
+      <c r="A57" s="249" t="s">
+        <v>202</v>
+      </c>
+      <c r="B57" s="250"/>
+      <c r="C57" s="250"/>
+      <c r="D57" s="250"/>
+      <c r="E57" s="250"/>
+      <c r="F57" s="250"/>
+      <c r="G57" s="250"/>
+      <c r="H57" s="250"/>
+      <c r="I57" s="250"/>
+      <c r="J57" s="251"/>
+      <c r="K57" s="249" t="s">
+        <v>203</v>
+      </c>
+      <c r="L57" s="250"/>
+      <c r="M57" s="251"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M4"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="L7:L11"/>
+    <mergeCell ref="L12:L15"/>
+    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="L27:L30"/>
+    <mergeCell ref="L31:L34"/>
+    <mergeCell ref="L35:L38"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="L41:L45"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="L47:L50"/>
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="K57:M57"/>
     <mergeCell ref="L51:L52"/>
@@ -10619,36 +10636,6 @@
     <mergeCell ref="K54:L54"/>
     <mergeCell ref="K55:L55"/>
     <mergeCell ref="K56:L56"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="L41:L45"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="L47:L50"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="L27:L30"/>
-    <mergeCell ref="L31:L34"/>
-    <mergeCell ref="L35:L38"/>
-    <mergeCell ref="L16:L19"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="K3:M4"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="L7:L11"/>
-    <mergeCell ref="L12:L15"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="L2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10674,15 +10661,15 @@
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
       <c r="E1" s="25"/>
-      <c r="F1" s="182" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="183"/>
+      <c r="F1" s="239" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="239"/>
+      <c r="H1" s="239"/>
+      <c r="I1" s="240"/>
       <c r="J1" s="24"/>
       <c r="K1" s="46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10693,87 +10680,87 @@
       <c r="E2" s="27"/>
       <c r="F2" s="27"/>
       <c r="G2" s="27"/>
-      <c r="H2" s="184" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" s="185"/>
+      <c r="H2" s="241" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="242"/>
       <c r="J2" s="26"/>
       <c r="K2" s="47" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="326" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="327"/>
+      <c r="C3" s="327"/>
+      <c r="D3" s="327"/>
+      <c r="E3" s="327"/>
+      <c r="F3" s="327"/>
+      <c r="G3" s="327"/>
+      <c r="H3" s="327"/>
+      <c r="I3" s="327"/>
+      <c r="J3" s="327"/>
+      <c r="K3" s="328"/>
+    </row>
+    <row r="4" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="316" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="317"/>
+      <c r="C4" s="316" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="288" t="s">
+      <c r="D4" s="317"/>
+      <c r="E4" s="316" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="289"/>
-      <c r="C3" s="289"/>
-      <c r="D3" s="289"/>
-      <c r="E3" s="289"/>
-      <c r="F3" s="289"/>
-      <c r="G3" s="289"/>
-      <c r="H3" s="289"/>
-      <c r="I3" s="289"/>
-      <c r="J3" s="289"/>
-      <c r="K3" s="290"/>
-    </row>
-    <row r="4" spans="1:11" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="291" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="292"/>
-      <c r="C4" s="291" t="s">
+      <c r="F4" s="317"/>
+      <c r="G4" s="316" t="s">
         <v>208</v>
       </c>
-      <c r="D4" s="292"/>
-      <c r="E4" s="291" t="s">
+      <c r="H4" s="317"/>
+      <c r="I4" s="316" t="s">
         <v>209</v>
       </c>
-      <c r="F4" s="292"/>
-      <c r="G4" s="291" t="s">
-        <v>210</v>
-      </c>
-      <c r="H4" s="292"/>
-      <c r="I4" s="291" t="s">
-        <v>211</v>
-      </c>
-      <c r="J4" s="292"/>
-      <c r="K4" s="293" t="s">
-        <v>8</v>
+      <c r="J4" s="317"/>
+      <c r="K4" s="324" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B5" s="81" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D5" s="81" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F5" s="81" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H5" s="81" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J5" s="81" t="s">
-        <v>213</v>
-      </c>
-      <c r="K5" s="294"/>
+        <v>211</v>
+      </c>
+      <c r="K5" s="325"/>
     </row>
     <row r="6" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="82">
@@ -10807,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -10842,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -10877,21 +10864,21 @@
         <v>0</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="295"/>
-      <c r="B9" s="296"/>
-      <c r="C9" s="296"/>
-      <c r="D9" s="296"/>
-      <c r="E9" s="296"/>
-      <c r="F9" s="296"/>
-      <c r="G9" s="296"/>
-      <c r="H9" s="296"/>
-      <c r="I9" s="296"/>
-      <c r="J9" s="296"/>
-      <c r="K9" s="297"/>
+      <c r="A9" s="307"/>
+      <c r="B9" s="308"/>
+      <c r="C9" s="308"/>
+      <c r="D9" s="308"/>
+      <c r="E9" s="308"/>
+      <c r="F9" s="308"/>
+      <c r="G9" s="308"/>
+      <c r="H9" s="308"/>
+      <c r="I9" s="308"/>
+      <c r="J9" s="308"/>
+      <c r="K9" s="309"/>
     </row>
     <row r="10" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="82">
@@ -10925,7 +10912,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -10960,21 +10947,21 @@
         <v>0</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="295"/>
-      <c r="B12" s="296"/>
-      <c r="C12" s="296"/>
-      <c r="D12" s="296"/>
-      <c r="E12" s="296"/>
-      <c r="F12" s="296"/>
-      <c r="G12" s="296"/>
-      <c r="H12" s="296"/>
-      <c r="I12" s="296"/>
-      <c r="J12" s="296"/>
-      <c r="K12" s="297"/>
+      <c r="A12" s="307"/>
+      <c r="B12" s="308"/>
+      <c r="C12" s="308"/>
+      <c r="D12" s="308"/>
+      <c r="E12" s="308"/>
+      <c r="F12" s="308"/>
+      <c r="G12" s="308"/>
+      <c r="H12" s="308"/>
+      <c r="I12" s="308"/>
+      <c r="J12" s="308"/>
+      <c r="K12" s="309"/>
     </row>
     <row r="13" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="82">
@@ -11008,7 +10995,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -11043,81 +11030,81 @@
         <v>0</v>
       </c>
       <c r="K14" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="313" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="314"/>
+      <c r="C15" s="314"/>
+      <c r="D15" s="314"/>
+      <c r="E15" s="314"/>
+      <c r="F15" s="314"/>
+      <c r="G15" s="314"/>
+      <c r="H15" s="314"/>
+      <c r="I15" s="314"/>
+      <c r="J15" s="314"/>
+      <c r="K15" s="315"/>
+    </row>
+    <row r="16" spans="1:11" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="316" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="317"/>
+      <c r="C16" s="318" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="298" t="s">
+      <c r="D16" s="319"/>
+      <c r="E16" s="316" t="s">
         <v>220</v>
       </c>
-      <c r="B15" s="299"/>
-      <c r="C15" s="299"/>
-      <c r="D15" s="299"/>
-      <c r="E15" s="299"/>
-      <c r="F15" s="299"/>
-      <c r="G15" s="299"/>
-      <c r="H15" s="299"/>
-      <c r="I15" s="299"/>
-      <c r="J15" s="299"/>
-      <c r="K15" s="300"/>
-    </row>
-    <row r="16" spans="1:11" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="291" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="292"/>
-      <c r="C16" s="301" t="s">
+      <c r="F16" s="317"/>
+      <c r="G16" s="320" t="s">
         <v>221</v>
       </c>
-      <c r="D16" s="302"/>
-      <c r="E16" s="291" t="s">
+      <c r="H16" s="321"/>
+      <c r="I16" s="322" t="s">
         <v>222</v>
       </c>
-      <c r="F16" s="292"/>
-      <c r="G16" s="303" t="s">
-        <v>223</v>
-      </c>
-      <c r="H16" s="304"/>
-      <c r="I16" s="305" t="s">
-        <v>224</v>
-      </c>
-      <c r="J16" s="306"/>
-      <c r="K16" s="293" t="s">
-        <v>8</v>
+      <c r="J16" s="323"/>
+      <c r="K16" s="324" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B17" s="81" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D17" s="81" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F17" s="81" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H17" s="81" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J17" s="81" t="s">
-        <v>213</v>
-      </c>
-      <c r="K17" s="294"/>
+        <v>211</v>
+      </c>
+      <c r="K17" s="325"/>
     </row>
     <row r="18" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="72">
@@ -11151,7 +11138,7 @@
         <v>21</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -11199,7 +11186,7 @@
         <v>6</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -11234,21 +11221,21 @@
         <v>0</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="295"/>
-      <c r="B22" s="296"/>
-      <c r="C22" s="296"/>
-      <c r="D22" s="296"/>
-      <c r="E22" s="296"/>
-      <c r="F22" s="296"/>
-      <c r="G22" s="296"/>
-      <c r="H22" s="296"/>
-      <c r="I22" s="296"/>
-      <c r="J22" s="296"/>
-      <c r="K22" s="297"/>
+      <c r="A22" s="307"/>
+      <c r="B22" s="308"/>
+      <c r="C22" s="308"/>
+      <c r="D22" s="308"/>
+      <c r="E22" s="308"/>
+      <c r="F22" s="308"/>
+      <c r="G22" s="308"/>
+      <c r="H22" s="308"/>
+      <c r="I22" s="308"/>
+      <c r="J22" s="308"/>
+      <c r="K22" s="309"/>
     </row>
     <row r="23" spans="1:11" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="82">
@@ -11282,7 +11269,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -11317,21 +11304,21 @@
         <v>0</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="295"/>
-      <c r="B25" s="296"/>
-      <c r="C25" s="296"/>
-      <c r="D25" s="296"/>
-      <c r="E25" s="296"/>
-      <c r="F25" s="296"/>
-      <c r="G25" s="296"/>
-      <c r="H25" s="296"/>
-      <c r="I25" s="296"/>
-      <c r="J25" s="296"/>
-      <c r="K25" s="297"/>
+      <c r="A25" s="307"/>
+      <c r="B25" s="308"/>
+      <c r="C25" s="308"/>
+      <c r="D25" s="308"/>
+      <c r="E25" s="308"/>
+      <c r="F25" s="308"/>
+      <c r="G25" s="308"/>
+      <c r="H25" s="308"/>
+      <c r="I25" s="308"/>
+      <c r="J25" s="308"/>
+      <c r="K25" s="309"/>
     </row>
     <row r="26" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="82">
@@ -11365,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -11400,50 +11387,54 @@
         <v>15</v>
       </c>
       <c r="K27" s="8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="62.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="119" t="s">
+        <v>225</v>
+      </c>
+      <c r="B28" s="120"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="121"/>
+      <c r="K28" s="50" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="20.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="310" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="62.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="124" t="s">
+      <c r="B29" s="311"/>
+      <c r="C29" s="311"/>
+      <c r="D29" s="311"/>
+      <c r="E29" s="311"/>
+      <c r="F29" s="312"/>
+      <c r="G29" s="310" t="s">
         <v>227</v>
       </c>
-      <c r="B28" s="125"/>
-      <c r="C28" s="125"/>
-      <c r="D28" s="125"/>
-      <c r="E28" s="125"/>
-      <c r="F28" s="125"/>
-      <c r="G28" s="125"/>
-      <c r="H28" s="125"/>
-      <c r="I28" s="125"/>
-      <c r="J28" s="126"/>
-      <c r="K28" s="50" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="20.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="307" t="s">
-        <v>228</v>
-      </c>
-      <c r="B29" s="308"/>
-      <c r="C29" s="308"/>
-      <c r="D29" s="308"/>
-      <c r="E29" s="308"/>
-      <c r="F29" s="309"/>
-      <c r="G29" s="307" t="s">
-        <v>229</v>
-      </c>
-      <c r="H29" s="308"/>
-      <c r="I29" s="308"/>
-      <c r="J29" s="308"/>
-      <c r="K29" s="309"/>
+      <c r="H29" s="311"/>
+      <c r="I29" s="311"/>
+      <c r="J29" s="311"/>
+      <c r="K29" s="312"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="G29:K29"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:K5"/>
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A15:K15"/>
@@ -11453,15 +11444,11 @@
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="K16:K17"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="G29:K29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11483,24 +11470,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="310" t="s">
-        <v>230</v>
-      </c>
-      <c r="B1" s="311"/>
+      <c r="A1" s="101" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="102"/>
       <c r="C1" s="24"/>
       <c r="D1" s="25"/>
       <c r="E1" s="25"/>
       <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="314" t="s">
+      <c r="G1" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="99"/>
+      <c r="H1" s="106"/>
     </row>
     <row r="2" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="312"/>
-      <c r="B2" s="313"/>
+      <c r="A2" s="103"/>
+      <c r="B2" s="104"/>
       <c r="C2" s="26"/>
       <c r="D2" s="27"/>
       <c r="E2" s="27"/>
@@ -11509,46 +11496,46 @@
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="83" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="107" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="109">
+        <v>1397</v>
+      </c>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="315" t="s">
+      <c r="G3" s="114" t="s">
         <v>232</v>
       </c>
-      <c r="B3" s="317">
-        <v>1397</v>
-      </c>
-      <c r="C3" s="318"/>
-      <c r="D3" s="318"/>
-      <c r="E3" s="319"/>
-      <c r="F3" s="320" t="s">
+      <c r="H3" s="107" t="s">
         <v>233</v>
       </c>
-      <c r="G3" s="322" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="108"/>
+      <c r="B4" s="80" t="s">
         <v>234</v>
       </c>
-      <c r="H3" s="315" t="s">
+      <c r="C4" s="84" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="316"/>
-      <c r="B4" s="80" t="s">
+      <c r="D4" s="80" t="s">
         <v>236</v>
       </c>
-      <c r="C4" s="84" t="s">
+      <c r="E4" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="D4" s="80" t="s">
-        <v>238</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="F4" s="321"/>
-      <c r="G4" s="323"/>
-      <c r="H4" s="316"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="108"/>
     </row>
     <row r="5" spans="1:8" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85">
@@ -11566,30 +11553,30 @@
       <c r="E5" s="85">
         <v>3323</v>
       </c>
-      <c r="F5" s="324" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="325"/>
-      <c r="H5" s="326"/>
+      <c r="F5" s="329" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="330"/>
+      <c r="H5" s="331"/>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="86">
         <v>4164</v>
       </c>
       <c r="B6" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D6" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E6" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F6" s="80" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G6" s="19">
         <v>1903023000</v>
@@ -11603,19 +11590,19 @@
         <v>1000</v>
       </c>
       <c r="B7" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D7" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F7" s="80" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G7" s="19">
         <v>1903023000</v>
@@ -11629,19 +11616,19 @@
         <v>2500</v>
       </c>
       <c r="B8" s="87" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>238</v>
+      </c>
+      <c r="D8" s="87" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" s="87" t="s">
+        <v>238</v>
+      </c>
+      <c r="F8" s="80" t="s">
         <v>240</v>
-      </c>
-      <c r="C8" s="87" t="s">
-        <v>240</v>
-      </c>
-      <c r="D8" s="87" t="s">
-        <v>240</v>
-      </c>
-      <c r="E8" s="87" t="s">
-        <v>240</v>
-      </c>
-      <c r="F8" s="80" t="s">
-        <v>242</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -11658,16 +11645,16 @@
         <v>1265</v>
       </c>
       <c r="C9" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D9" s="86">
         <v>1265</v>
       </c>
       <c r="E9" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F9" s="80" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G9" s="19">
         <v>1805013000</v>
@@ -11678,22 +11665,22 @@
     </row>
     <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B10" s="86">
         <v>3500</v>
       </c>
       <c r="C10" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D10" s="86">
         <v>3500</v>
       </c>
       <c r="E10" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F10" s="80" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G10" s="19">
         <v>1804014000</v>
@@ -11704,7 +11691,7 @@
     </row>
     <row r="11" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B11" s="88">
         <v>33</v>
@@ -11713,13 +11700,13 @@
         <v>161</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E11" s="88">
         <v>194</v>
       </c>
       <c r="F11" s="80" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G11" s="19">
         <v>1805021000</v>
@@ -11733,19 +11720,19 @@
         <v>9000</v>
       </c>
       <c r="B12" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D12" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E12" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G12" s="19">
         <v>1805021000</v>
@@ -11771,7 +11758,7 @@
         <v>1560</v>
       </c>
       <c r="F13" s="80" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G13" s="19">
         <v>1805016000</v>
@@ -11797,7 +11784,7 @@
         <v>232</v>
       </c>
       <c r="F14" s="80" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G14" s="19">
         <v>1805005000</v>
@@ -11811,19 +11798,19 @@
         <v>29700</v>
       </c>
       <c r="B15" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D15" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E15" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F15" s="80" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -11834,22 +11821,22 @@
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B16" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C16" s="88">
         <v>102</v>
       </c>
       <c r="D16" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E16" s="88">
         <v>102</v>
       </c>
       <c r="F16" s="80" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G16" s="19">
         <v>1804011000</v>
@@ -11869,13 +11856,13 @@
         <v>180</v>
       </c>
       <c r="D17" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E17" s="86">
         <v>1235</v>
       </c>
       <c r="F17" s="80" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -11886,19 +11873,19 @@
     </row>
     <row r="18" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B18" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C18" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D18" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E18" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F18" s="19">
         <v>0</v>
@@ -11912,19 +11899,19 @@
     </row>
     <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B19" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D19" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E19" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F19" s="19">
         <v>0</v>
@@ -11938,19 +11925,19 @@
     </row>
     <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B20" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D20" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E20" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F20" s="19">
         <v>0</v>
@@ -11963,30 +11950,30 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="107.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="159"/>
-      <c r="B21" s="160"/>
-      <c r="C21" s="160"/>
-      <c r="D21" s="160"/>
-      <c r="E21" s="160"/>
-      <c r="F21" s="160"/>
-      <c r="G21" s="161"/>
+      <c r="A21" s="95"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="97"/>
       <c r="H21" s="89" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="327" t="s">
-        <v>251</v>
-      </c>
-      <c r="B22" s="328"/>
-      <c r="C22" s="328"/>
-      <c r="D22" s="328"/>
-      <c r="E22" s="329"/>
-      <c r="F22" s="327" t="s">
-        <v>252</v>
-      </c>
-      <c r="G22" s="328"/>
-      <c r="H22" s="329"/>
+      <c r="A22" s="98" t="s">
+        <v>249</v>
+      </c>
+      <c r="B22" s="99"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="98" t="s">
+        <v>250</v>
+      </c>
+      <c r="G22" s="99"/>
+      <c r="H22" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -12022,24 +12009,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="310" t="s">
-        <v>230</v>
-      </c>
-      <c r="B1" s="311"/>
+      <c r="A1" s="101" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="102"/>
       <c r="C1" s="24"/>
       <c r="D1" s="25"/>
       <c r="E1" s="25"/>
       <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="314" t="s">
+      <c r="G1" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="99"/>
+      <c r="H1" s="106"/>
     </row>
     <row r="2" spans="1:8" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="312"/>
-      <c r="B2" s="313"/>
+      <c r="A2" s="103"/>
+      <c r="B2" s="104"/>
       <c r="C2" s="26"/>
       <c r="D2" s="27"/>
       <c r="E2" s="27"/>
@@ -12048,46 +12035,46 @@
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="83" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="315" t="s">
+      <c r="A3" s="107" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="109">
+        <v>1397</v>
+      </c>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="112" t="s">
+        <v>231</v>
+      </c>
+      <c r="G3" s="114" t="s">
         <v>232</v>
       </c>
-      <c r="B3" s="317">
-        <v>1397</v>
-      </c>
-      <c r="C3" s="318"/>
-      <c r="D3" s="318"/>
-      <c r="E3" s="319"/>
-      <c r="F3" s="320" t="s">
+      <c r="H3" s="107" t="s">
         <v>233</v>
       </c>
-      <c r="G3" s="322" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="108"/>
+      <c r="B4" s="80" t="s">
         <v>234</v>
       </c>
-      <c r="H3" s="315" t="s">
+      <c r="C4" s="84" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="316"/>
-      <c r="B4" s="80" t="s">
+      <c r="D4" s="80" t="s">
         <v>236</v>
       </c>
-      <c r="C4" s="84" t="s">
+      <c r="E4" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="D4" s="80" t="s">
-        <v>238</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="F4" s="321"/>
-      <c r="G4" s="323"/>
-      <c r="H4" s="316"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="108"/>
     </row>
     <row r="5" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="90">
@@ -12105,11 +12092,11 @@
       <c r="E5" s="90">
         <v>5066</v>
       </c>
-      <c r="F5" s="330" t="s">
-        <v>254</v>
-      </c>
-      <c r="G5" s="331"/>
-      <c r="H5" s="332"/>
+      <c r="F5" s="92" t="s">
+        <v>252</v>
+      </c>
+      <c r="G5" s="93"/>
+      <c r="H5" s="94"/>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="88">
@@ -12128,7 +12115,7 @@
         <v>1208</v>
       </c>
       <c r="F6" s="80" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G6" s="19">
         <v>1804014001</v>
@@ -12145,16 +12132,16 @@
         <v>11000</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D7" s="86">
         <v>11000</v>
       </c>
       <c r="E7" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F7" s="80" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G7" s="19">
         <v>1804014001</v>
@@ -12168,19 +12155,19 @@
         <v>3000</v>
       </c>
       <c r="B8" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C8" s="88">
         <v>31</v>
       </c>
       <c r="D8" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E8" s="88">
         <v>31</v>
       </c>
       <c r="F8" s="80" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G8" s="19">
         <v>1804011051</v>
@@ -12191,22 +12178,22 @@
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B9" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C9" s="86">
         <v>1500</v>
       </c>
       <c r="D9" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E9" s="86">
         <v>1500</v>
       </c>
       <c r="F9" s="80" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G9" s="19">
         <v>113579</v>
@@ -12217,7 +12204,7 @@
     </row>
     <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B10" s="88">
         <v>814</v>
@@ -12226,13 +12213,13 @@
         <v>1513</v>
       </c>
       <c r="D10" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E10" s="86">
         <v>2327</v>
       </c>
       <c r="F10" s="80" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G10" s="19">
         <v>0</v>
@@ -12243,19 +12230,19 @@
     </row>
     <row r="11" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B11" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E11" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F11" s="19">
         <v>0</v>
@@ -12269,19 +12256,19 @@
     </row>
     <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B12" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D12" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E12" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F12" s="19">
         <v>0</v>
@@ -12295,19 +12282,19 @@
     </row>
     <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B13" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D13" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E13" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F13" s="19">
         <v>0</v>
@@ -12321,19 +12308,19 @@
     </row>
     <row r="14" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B14" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D14" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E14" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F14" s="19">
         <v>0</v>
@@ -12347,19 +12334,19 @@
     </row>
     <row r="15" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B15" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D15" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E15" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F15" s="19">
         <v>0</v>
@@ -12373,19 +12360,19 @@
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B16" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D16" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E16" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F16" s="19">
         <v>0</v>
@@ -12399,19 +12386,19 @@
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B17" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C17" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D17" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E17" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F17" s="19">
         <v>0</v>
@@ -12425,19 +12412,19 @@
     </row>
     <row r="18" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B18" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C18" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D18" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E18" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F18" s="19">
         <v>0</v>
@@ -12451,19 +12438,19 @@
     </row>
     <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B19" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D19" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E19" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F19" s="19">
         <v>0</v>
@@ -12477,19 +12464,19 @@
     </row>
     <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B20" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D20" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E20" s="87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F20" s="19">
         <v>0</v>
@@ -12502,30 +12489,30 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="107.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="159"/>
-      <c r="B21" s="160"/>
-      <c r="C21" s="160"/>
-      <c r="D21" s="160"/>
-      <c r="E21" s="160"/>
-      <c r="F21" s="160"/>
-      <c r="G21" s="161"/>
+      <c r="A21" s="95"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="97"/>
       <c r="H21" s="91" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="327" t="s">
-        <v>251</v>
-      </c>
-      <c r="B22" s="328"/>
-      <c r="C22" s="328"/>
-      <c r="D22" s="328"/>
-      <c r="E22" s="329"/>
-      <c r="F22" s="327" t="s">
-        <v>252</v>
-      </c>
-      <c r="G22" s="328"/>
-      <c r="H22" s="329"/>
+      <c r="A22" s="98" t="s">
+        <v>249</v>
+      </c>
+      <c r="B22" s="99"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="100"/>
+      <c r="F22" s="98" t="s">
+        <v>250</v>
+      </c>
+      <c r="G22" s="99"/>
+      <c r="H22" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="11">
